--- a/users.xlsx
+++ b/users.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="165">
   <si>
     <t>S NO</t>
   </si>
@@ -47,6 +47,9 @@
     <t>BRANCH</t>
   </si>
   <si>
+    <t>LEETCODE</t>
+  </si>
+  <si>
     <t>ADMIN</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
   </si>
   <si>
     <t>A22126552006</t>
+  </si>
+  <si>
+    <t>leetcode.com/u/sriharshini_02</t>
   </si>
   <si>
     <t>ARYAN MODA RAJ BODANKI</t>
@@ -528,7 +534,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,13 +556,6 @@
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -991,19 +990,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1012,7 +1011,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1021,125 +1023,123 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1459,16 +1459,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.09090909090909" customWidth="1"/>
     <col min="2" max="2" width="28.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="38.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="20.5454545454545" customWidth="1"/>
+    <col min="7" max="7" width="53.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1486,6 +1487,9 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1493,16 +1497,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1510,16 +1514,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1527,16 +1531,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1544,16 +1548,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1561,19 +1565,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1581,19 +1585,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1601,19 +1605,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1621,19 +1625,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1641,19 +1645,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1661,39 +1665,42 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
         <v>36</v>
       </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1701,19 +1708,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1721,19 +1728,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1741,19 +1748,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1761,19 +1768,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1781,19 +1788,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1801,19 +1808,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1821,19 +1828,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
         <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1841,19 +1848,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1861,19 +1868,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1881,19 +1888,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1901,19 +1908,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1921,19 +1928,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1941,19 +1948,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1961,19 +1968,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1981,19 +1988,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2001,19 +2008,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2021,19 +2028,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2041,19 +2048,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
         <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2061,19 +2068,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2081,19 +2088,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2101,19 +2108,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2121,19 +2128,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2141,19 +2148,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2161,19 +2168,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2181,19 +2188,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2201,19 +2208,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2221,19 +2228,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2241,19 +2248,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2261,19 +2268,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2281,19 +2288,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2301,19 +2308,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2321,19 +2328,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2341,19 +2348,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2361,19 +2368,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2381,19 +2388,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2401,19 +2408,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2421,19 +2428,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C49" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2441,19 +2448,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2461,19 +2468,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2481,19 +2488,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2501,19 +2508,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D53" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:1">
@@ -2533,6 +2540,7 @@
     <hyperlink ref="C4" r:id="rId3" display="staff2@nexthire.com"/>
     <hyperlink ref="C5" r:id="rId4" display="staff3@nexthire.com"/>
     <hyperlink ref="C7" r:id="rId5" display="A22126552001@nexthire.com"/>
+    <hyperlink ref="C12" r:id="rId6" display="A22126552006@nexthire.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/users.xlsx
+++ b/users.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="168">
   <si>
     <t>S NO</t>
   </si>
@@ -522,6 +522,15 @@
   </si>
   <si>
     <t>A22126552030</t>
+  </si>
+  <si>
+    <t>TEST STUDENT</t>
+  </si>
+  <si>
+    <t>test@nexthire.com</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -1135,11 +1144,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1567,7 +1577,7 @@
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
@@ -1627,7 +1637,7 @@
       <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
@@ -1667,7 +1677,7 @@
       <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D11" t="s">
@@ -1687,7 +1697,7 @@
       <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D12" t="s">
@@ -2523,9 +2533,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" t="s">
+        <v>167</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -2535,12 +2560,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="admin@nexthire.com"/>
+    <hyperlink ref="C2" r:id="rId1" display="admin@nexthire.com" tooltip="mailto:admin@nexthire.com"/>
     <hyperlink ref="C3" r:id="rId2" display="staff1@nexthire.com" tooltip="mailto:staff1@nexthire.com"/>
     <hyperlink ref="C4" r:id="rId3" display="staff2@nexthire.com"/>
     <hyperlink ref="C5" r:id="rId4" display="staff3@nexthire.com"/>
     <hyperlink ref="C7" r:id="rId5" display="A22126552001@nexthire.com"/>
     <hyperlink ref="C12" r:id="rId6" display="A22126552006@nexthire.com"/>
+    <hyperlink ref="C6" r:id="rId7" display="chodipilliajaykumar.22.csm@anits.edu.in"/>
+    <hyperlink ref="C9" r:id="rId8" display="A22126552003@nexthire.com"/>
+    <hyperlink ref="C54" r:id="rId9" display="test@nexthire.com"/>
+    <hyperlink ref="C11" r:id="rId10" display="A22126552005@nexthire.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
